--- a/Arquivo.xlsx
+++ b/Arquivo.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="Usuarios" sheetId="1" state="visible" r:id="rId3"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="283" uniqueCount="151">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="285" uniqueCount="152">
   <si>
     <t xml:space="preserve">id_user</t>
   </si>
@@ -78,109 +78,112 @@
     <t xml:space="preserve">data_final</t>
   </si>
   <si>
+    <t xml:space="preserve">local</t>
+  </si>
+  <si>
+    <t xml:space="preserve">organizador</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Semana de Computação</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Palestras e workshops de TI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Auditório ICEx - UFMG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UFMG / PET Computação</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hackathon UFMG 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Maratona de programação 48h</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Centro de Inovação UFMG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IEEE UFMG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Congresso de Engenharia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Apresentação de trabalhos científicos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Escola de Engenharia - UFMG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DEE / UFMG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Workshop de IA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Introdução prática a Machine Learning</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Laboratório de Dados - UFMG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lab IA UFMG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">id_semestre</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ano</t>
+  </si>
+  <si>
+    <t xml:space="preserve">semestre_num</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ativo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ciência da Computação - UFMG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">True</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">False</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Engenharia Elétrica - UFMG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">id_materia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">professor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sala</t>
+  </si>
+  <si>
     <t xml:space="preserve">horario</t>
-  </si>
-  <si>
-    <t xml:space="preserve">local</t>
-  </si>
-  <si>
-    <t xml:space="preserve">organizador</t>
-  </si>
-  <si>
-    <t xml:space="preserve">E001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Semana de Computação</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Palestras e workshops de TI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">09:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Auditório ICEx - UFMG</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UFMG / PET Computação</t>
-  </si>
-  <si>
-    <t xml:space="preserve">E002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hackathon UFMG 2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Maratona de programação 48h</t>
-  </si>
-  <si>
-    <t xml:space="preserve">08:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Centro de Inovação UFMG</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IEEE UFMG</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Congresso de Engenharia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Apresentação de trabalhos científicos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">08:30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Escola de Engenharia - UFMG</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DEE / UFMG</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Workshop de IA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Introdução prática a Machine Learning</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Laboratório de Dados - UFMG</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lab IA UFMG</t>
-  </si>
-  <si>
-    <t xml:space="preserve">id_semestre</t>
-  </si>
-  <si>
-    <t xml:space="preserve">S001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ciência da Computação - UFMG</t>
-  </si>
-  <si>
-    <t xml:space="preserve">S002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Engenharia Elétrica - UFMG</t>
-  </si>
-  <si>
-    <t xml:space="preserve">id_materia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">professor</t>
-  </si>
-  <si>
-    <t xml:space="preserve">sala</t>
   </si>
   <si>
     <t xml:space="preserve">M001</t>
@@ -593,44 +596,32 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="7">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -889,51 +880,51 @@
   <dimension ref="A1:D3"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="23"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="23"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="15"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="3" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="3" t="s">
+      <c r="A3" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="D3" s="4" t="s">
         <v>11</v>
       </c>
     </row>
@@ -953,162 +944,147 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:I5"/>
+  <dimension ref="A1:H5"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="0" width="27"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="40"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="31"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="25"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="1" width="27"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="40"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="31"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="25"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16384" style="0" width="11.53"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="I1" s="1" t="s">
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
+      <c r="C2" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="E2" s="5" t="n">
+        <v>46266</v>
+      </c>
+      <c r="F2" s="5" t="n">
+        <v>46270</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="E2" s="4" t="n">
-        <v>46266</v>
-      </c>
-      <c r="F2" s="4" t="n">
-        <v>46270</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="H2" s="2" t="s">
+      <c r="B3" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="I2" s="2" t="s">
+      <c r="C3" s="4" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3" s="3" t="s">
+      <c r="D3" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="E3" s="6" t="n">
+        <v>46305</v>
+      </c>
+      <c r="F3" s="6" t="n">
+        <v>46307</v>
+      </c>
+      <c r="G3" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="H3" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="E3" s="5" t="n">
-        <v>46305</v>
-      </c>
-      <c r="F3" s="5" t="n">
-        <v>46307</v>
-      </c>
-      <c r="G3" s="3" t="s">
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C4" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="H3" s="3" t="s">
+      <c r="D4" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="I3" s="3" t="s">
+      <c r="E4" s="5" t="n">
+        <v>46249</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>46251</v>
+      </c>
+      <c r="G4" s="3" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="2" t="s">
+      <c r="H4" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="B4" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="D4" s="2" t="s">
+      <c r="B5" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="C5" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="E4" s="4" t="n">
-        <v>46249</v>
-      </c>
-      <c r="F4" s="4" t="n">
-        <v>46251</v>
-      </c>
-      <c r="G4" s="2" t="s">
+      <c r="D5" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="H4" s="2" t="s">
+      <c r="E5" s="6" t="n">
+        <v>46329</v>
+      </c>
+      <c r="F5" s="6" t="n">
+        <v>46329</v>
+      </c>
+      <c r="G5" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="I4" s="2" t="s">
+      <c r="H5" s="4" t="s">
         <v>36</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="E5" s="5" t="n">
-        <v>46329</v>
-      </c>
-      <c r="F5" s="5" t="n">
-        <v>46329</v>
-      </c>
-      <c r="G5" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="H5" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="I5" s="3" t="s">
-        <v>41</v>
       </c>
     </row>
   </sheetData>
@@ -1127,83 +1103,131 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="15.72"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="32"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="15.72"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="32"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="8.68"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="17.39"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="8.68"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C2" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
+      <c r="D2" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E2" s="3" t="n">
+        <v>2026</v>
+      </c>
+      <c r="F2" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B3" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="D3" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="E3" s="4" t="n">
+        <v>2026</v>
+      </c>
+      <c r="F3" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="E4" s="3" t="n">
+        <v>2026</v>
+      </c>
+      <c r="F4" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G4" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="D2" s="2" t="s">
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" s="4" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3" s="3" t="s">
+      <c r="C5" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="D5" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="E5" s="4" t="n">
+        <v>2026</v>
+      </c>
+      <c r="F5" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="G5" s="4" t="s">
         <v>47</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>48</v>
       </c>
     </row>
   </sheetData>
@@ -1225,247 +1249,247 @@
   <dimension ref="A1:H9"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="36"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="40"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="25"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="7" style="0" width="19"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="36"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="40"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="25"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="7" style="1" width="19"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="C1" s="1" t="s">
+      <c r="B1" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C1" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="H1" s="1" t="s">
-        <v>17</v>
+      <c r="H1" s="2" t="s">
+        <v>52</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="D2" s="2" t="s">
+      <c r="B2" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C2" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="D2" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="E2" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="F2" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="G2" s="3" t="s">
         <v>57</v>
       </c>
+      <c r="H2" s="3" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="3" t="s">
+      <c r="A3" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="D3" s="3" t="s">
+      <c r="B3" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="C3" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="D3" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="E3" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="G3" s="3" t="s">
+      <c r="F3" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="H3" s="3" t="s">
+      <c r="G3" s="4" t="s">
         <v>63</v>
       </c>
+      <c r="H3" s="4" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="2" t="s">
+      <c r="A4" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="D4" s="2" t="s">
+      <c r="B4" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="C4" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="D4" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="F4" s="2" t="s">
+      <c r="E4" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="G4" s="2" t="s">
+      <c r="F4" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="H4" s="2" t="s">
+      <c r="G4" s="3" t="s">
         <v>69</v>
       </c>
+      <c r="H4" s="3" t="s">
+        <v>70</v>
+      </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="3" t="s">
+      <c r="A5" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="D5" s="3" t="s">
+      <c r="B5" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="C5" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="E5" s="3" t="s">
+      <c r="D5" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="F5" s="3" t="s">
+      <c r="E5" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="G5" s="3" t="s">
+      <c r="F5" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="H5" s="3" t="s">
+      <c r="G5" s="4" t="s">
         <v>75</v>
       </c>
+      <c r="H5" s="4" t="s">
+        <v>76</v>
+      </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="2" t="s">
+      <c r="A6" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B6" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="E6" s="2" t="s">
+      <c r="B6" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="D6" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="F6" s="2" t="s">
+      <c r="E6" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="G6" s="2" t="s">
+      <c r="F6" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="H6" s="2" t="s">
+      <c r="G6" s="3" t="s">
         <v>80</v>
       </c>
+      <c r="H6" s="3" t="s">
+        <v>81</v>
+      </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="3" t="s">
+      <c r="A7" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="B7" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="E7" s="3" t="s">
+      <c r="B7" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="D7" s="4" t="s">
         <v>82</v>
       </c>
-      <c r="F7" s="3" t="s">
+      <c r="E7" s="4" t="s">
         <v>83</v>
       </c>
-      <c r="G7" s="3" t="s">
+      <c r="F7" s="4" t="s">
         <v>84</v>
       </c>
-      <c r="H7" s="3" t="s">
+      <c r="G7" s="4" t="s">
         <v>85</v>
       </c>
+      <c r="H7" s="4" t="s">
+        <v>86</v>
+      </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="2" t="s">
+      <c r="A8" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B8" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="E8" s="2" t="s">
+      <c r="B8" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="D8" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="F8" s="2" t="s">
+      <c r="E8" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="G8" s="2" t="s">
+      <c r="F8" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="H8" s="2" t="s">
+      <c r="G8" s="3" t="s">
         <v>90</v>
       </c>
+      <c r="H8" s="3" t="s">
+        <v>91</v>
+      </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="3" t="s">
+      <c r="A9" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="B9" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="E9" s="3" t="s">
+      <c r="B9" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="D9" s="4" t="s">
         <v>92</v>
       </c>
-      <c r="F9" s="3" t="s">
+      <c r="E9" s="4" t="s">
         <v>93</v>
       </c>
-      <c r="G9" s="3" t="s">
+      <c r="F9" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="H9" s="3" t="s">
+      <c r="G9" s="4" t="s">
         <v>95</v>
+      </c>
+      <c r="H9" s="4" t="s">
+        <v>96</v>
       </c>
     </row>
   </sheetData>
@@ -1487,330 +1511,330 @@
   <dimension ref="A1:K9"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="3" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="24"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="40"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="19"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="3" style="1" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="40"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="19"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="11"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="C1" s="1" t="s">
+      <c r="B1" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C1" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="E1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="F1" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="G1" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="H1" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="I1" s="1" t="s">
+      <c r="H1" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="I1" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="J1" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="K1" s="1" t="s">
-        <v>101</v>
+      <c r="K1" s="2" t="s">
+        <v>102</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="E2" s="2" t="n">
+      <c r="B2" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="E2" s="3" t="n">
         <v>40</v>
       </c>
-      <c r="F2" s="2" t="n">
+      <c r="F2" s="3" t="n">
         <v>35.5</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="G2" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="H2" s="5" t="n">
+        <v>46127</v>
+      </c>
+      <c r="I2" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="J2" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="K2" s="3" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="D3" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="H2" s="4" t="n">
-        <v>46127</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="J2" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="K2" s="2" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="3" t="s">
+      <c r="E3" s="4" t="n">
+        <v>40</v>
+      </c>
+      <c r="F3" s="4" t="n">
+        <v>38</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="H3" s="6" t="n">
+        <v>46130</v>
+      </c>
+      <c r="I3" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="J3" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="K3" s="4" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="E3" s="3" t="n">
+      <c r="B4" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="E4" s="3" t="n">
         <v>40</v>
       </c>
-      <c r="F3" s="3" t="n">
-        <v>38</v>
-      </c>
-      <c r="G3" s="3" t="s">
+      <c r="F4" s="3" t="n">
+        <v>36</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="H4" s="5" t="n">
+        <v>46285</v>
+      </c>
+      <c r="I4" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="J4" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="K4" s="3" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="E5" s="4" t="n">
+        <v>40</v>
+      </c>
+      <c r="F5" s="4" t="n">
+        <v>32</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="H5" s="6" t="n">
+        <v>46287</v>
+      </c>
+      <c r="I5" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="J5" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="K5" s="4" t="s">
         <v>106</v>
       </c>
-      <c r="H3" s="5" t="n">
-        <v>46130</v>
-      </c>
-      <c r="I3" s="3" t="s">
-        <v>107</v>
-      </c>
-      <c r="J3" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="K3" s="3" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B4" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="E4" s="2" t="n">
-        <v>40</v>
-      </c>
-      <c r="F4" s="2" t="n">
-        <v>36</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="H4" s="4" t="n">
-        <v>46285</v>
-      </c>
-      <c r="I4" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="J4" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="K4" s="2" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B5" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="E5" s="3" t="n">
-        <v>40</v>
-      </c>
-      <c r="F5" s="3" t="n">
-        <v>32</v>
-      </c>
-      <c r="G5" s="3" t="s">
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="F6" s="3" t="n">
+        <v>45</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="H6" s="5" t="n">
+        <v>46124</v>
+      </c>
+      <c r="I6" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="J6" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="K6" s="3" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="E7" s="4" t="n">
+        <v>50</v>
+      </c>
+      <c r="F7" s="4" t="n">
+        <v>42.5</v>
+      </c>
+      <c r="G7" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>46132</v>
+      </c>
+      <c r="I7" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="J7" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="K7" s="4" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="E8" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="F8" s="3" t="n">
+        <v>47</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="H8" s="5" t="n">
+        <v>46283</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="J8" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="K8" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="H5" s="5" t="n">
-        <v>46287</v>
-      </c>
-      <c r="I5" s="3" t="s">
-        <v>112</v>
-      </c>
-      <c r="J5" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="K5" s="3" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="2" t="s">
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="B6" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="E6" s="2" t="n">
+      <c r="B9" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="E9" s="4" t="n">
         <v>50</v>
       </c>
-      <c r="F6" s="2" t="n">
-        <v>45</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="H6" s="4" t="n">
-        <v>46124</v>
-      </c>
-      <c r="I6" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="J6" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="K6" s="2" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B7" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="E7" s="3" t="n">
-        <v>50</v>
-      </c>
-      <c r="F7" s="3" t="n">
-        <v>42.5</v>
-      </c>
-      <c r="G7" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="H7" s="5" t="n">
-        <v>46132</v>
-      </c>
-      <c r="I7" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="J7" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="K7" s="3" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B8" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="E8" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="F8" s="2" t="n">
-        <v>47</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="H8" s="4" t="n">
-        <v>46283</v>
-      </c>
-      <c r="I8" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="J8" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="K8" s="2" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B9" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="E9" s="3" t="n">
-        <v>50</v>
-      </c>
-      <c r="F9" s="3" t="n">
+      <c r="F9" s="4" t="n">
         <v>44</v>
       </c>
-      <c r="G9" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="H9" s="5" t="n">
+      <c r="G9" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="H9" s="6" t="n">
         <v>46290</v>
       </c>
-      <c r="I9" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="J9" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="K9" s="3" t="s">
-        <v>110</v>
+      <c r="I9" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="J9" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="K9" s="4" t="s">
+        <v>111</v>
       </c>
     </row>
   </sheetData>
@@ -1832,328 +1856,328 @@
   <dimension ref="A1:K9"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="3" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="31"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="40"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="33"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="3" style="1" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="31"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="40"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="33"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="12"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="C1" s="1" t="s">
+      <c r="B1" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C1" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="F1" s="1" t="s">
+      <c r="D1" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="E1" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="F1" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="G1" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="H1" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="I1" s="1" t="s">
+      <c r="H1" s="2" t="s">
         <v>124</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="I1" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="J1" s="2" t="s">
         <v>126</v>
       </c>
+      <c r="K1" s="2" t="s">
+        <v>127</v>
+      </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="E2" s="2" t="n">
+      <c r="B2" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E2" s="3" t="n">
         <v>30</v>
       </c>
-      <c r="F2" s="2" t="n">
+      <c r="F2" s="3" t="n">
         <v>27</v>
       </c>
-      <c r="G2" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="H2" s="4" t="n">
+      <c r="G2" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="H2" s="5" t="n">
         <v>46152</v>
       </c>
-      <c r="I2" s="2" t="s">
-        <v>129</v>
-      </c>
-      <c r="J2" s="2" t="s">
+      <c r="I2" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="K2" s="8" t="b">
+      <c r="J2" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="K2" s="3" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="3" t="s">
+      <c r="A3" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="E3" s="3" t="n">
+      <c r="B3" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E3" s="4" t="n">
         <v>30</v>
       </c>
-      <c r="F3" s="3" t="n">
+      <c r="F3" s="4" t="n">
         <v>29</v>
       </c>
-      <c r="G3" s="3" t="s">
-        <v>131</v>
-      </c>
-      <c r="H3" s="5" t="n">
+      <c r="G3" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="H3" s="6" t="n">
         <v>46162</v>
       </c>
-      <c r="I3" s="3" t="s">
-        <v>132</v>
-      </c>
-      <c r="J3" s="3" t="s">
+      <c r="I3" s="4" t="s">
         <v>133</v>
       </c>
-      <c r="K3" s="9" t="b">
+      <c r="J3" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="K3" s="4" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="2" t="s">
+      <c r="A4" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="E4" s="2" t="n">
+      <c r="B4" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E4" s="3" t="n">
         <v>30</v>
       </c>
-      <c r="F4" s="2"/>
-      <c r="G4" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="H4" s="4" t="n">
+      <c r="F4" s="3"/>
+      <c r="G4" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="H4" s="5" t="n">
         <v>46310</v>
       </c>
-      <c r="I4" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="J4" s="2" t="s">
+      <c r="I4" s="3" t="s">
         <v>136</v>
       </c>
-      <c r="K4" s="8" t="b">
+      <c r="J4" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="K4" s="3" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="3" t="s">
+      <c r="A5" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="E5" s="3" t="n">
+      <c r="B5" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E5" s="4" t="n">
         <v>30</v>
       </c>
-      <c r="F5" s="3"/>
-      <c r="G5" s="3" t="s">
-        <v>137</v>
-      </c>
-      <c r="H5" s="5" t="n">
+      <c r="F5" s="4"/>
+      <c r="G5" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="H5" s="6" t="n">
         <v>46320</v>
       </c>
-      <c r="I5" s="3" t="s">
-        <v>138</v>
-      </c>
-      <c r="J5" s="3" t="s">
+      <c r="I5" s="4" t="s">
         <v>139</v>
       </c>
-      <c r="K5" s="9" t="b">
+      <c r="J5" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="K5" s="4" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="2" t="s">
+      <c r="A6" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B6" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="E6" s="2" t="n">
+      <c r="B6" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E6" s="3" t="n">
         <v>30</v>
       </c>
-      <c r="F6" s="2" t="n">
+      <c r="F6" s="3" t="n">
         <v>28.5</v>
       </c>
-      <c r="G6" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="H6" s="4" t="n">
+      <c r="G6" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="H6" s="5" t="n">
         <v>46147</v>
       </c>
-      <c r="I6" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="J6" s="2" t="s">
+      <c r="I6" s="3" t="s">
         <v>142</v>
       </c>
-      <c r="K6" s="8" t="b">
+      <c r="J6" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="K6" s="3" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="3" t="s">
+      <c r="A7" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="B7" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="E7" s="3" t="n">
+      <c r="B7" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E7" s="4" t="n">
         <v>30</v>
       </c>
-      <c r="F7" s="3" t="n">
+      <c r="F7" s="4" t="n">
         <v>25</v>
       </c>
-      <c r="G7" s="3" t="s">
-        <v>143</v>
-      </c>
-      <c r="H7" s="5" t="n">
+      <c r="G7" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="H7" s="6" t="n">
         <v>46160</v>
       </c>
-      <c r="I7" s="3" t="s">
-        <v>144</v>
-      </c>
-      <c r="J7" s="3" t="s">
-        <v>139</v>
-      </c>
-      <c r="K7" s="9" t="b">
+      <c r="I7" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="J7" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="K7" s="4" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="2" t="s">
+      <c r="A8" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B8" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="E8" s="2" t="n">
+      <c r="B8" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E8" s="3" t="n">
         <v>30</v>
       </c>
-      <c r="F8" s="2"/>
-      <c r="G8" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="H8" s="4" t="n">
+      <c r="F8" s="3"/>
+      <c r="G8" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="H8" s="5" t="n">
         <v>46315</v>
       </c>
-      <c r="I8" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="J8" s="2" t="s">
+      <c r="I8" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="K8" s="8" t="b">
+      <c r="J8" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="K8" s="3" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="3" t="s">
+      <c r="A9" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="B9" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="E9" s="3" t="n">
+      <c r="B9" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E9" s="4" t="n">
         <v>30</v>
       </c>
-      <c r="F9" s="3"/>
-      <c r="G9" s="3" t="s">
-        <v>148</v>
-      </c>
-      <c r="H9" s="5" t="n">
+      <c r="F9" s="4"/>
+      <c r="G9" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="H9" s="6" t="n">
         <v>46331</v>
       </c>
-      <c r="I9" s="3" t="s">
-        <v>149</v>
-      </c>
-      <c r="J9" s="3" t="s">
+      <c r="I9" s="4" t="s">
         <v>150</v>
       </c>
-      <c r="K9" s="9" t="b">
+      <c r="J9" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="K9" s="4" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>

--- a/Arquivo.xlsx
+++ b/Arquivo.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="4"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="Usuarios" sheetId="1" state="visible" r:id="rId3"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="285" uniqueCount="152">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="293" uniqueCount="152">
   <si>
     <t xml:space="preserve">id_user</t>
   </si>
@@ -487,9 +487,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="166" formatCode="&quot;VERDADEIRO&quot;;&quot;VERDADEIRO&quot;;&quot;FALSO&quot;"/>
   </numFmts>
   <fonts count="6">
     <font>
@@ -596,7 +597,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -622,6 +623,14 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="165" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -954,7 +963,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="14"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="31"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="25"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16384" style="0" width="11.53"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16384" style="1" width="11.53"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1933,9 +1942,8 @@
       <c r="J2" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="K2" s="3" t="b">
-        <f aca="false">TRUE()</f>
-        <v>1</v>
+      <c r="K2" s="7" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1969,9 +1977,8 @@
       <c r="J3" s="4" t="s">
         <v>134</v>
       </c>
-      <c r="K3" s="4" t="b">
-        <f aca="false">TRUE()</f>
-        <v>1</v>
+      <c r="K3" s="8" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2003,9 +2010,8 @@
       <c r="J4" s="3" t="s">
         <v>137</v>
       </c>
-      <c r="K4" s="3" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
+      <c r="K4" s="7" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2037,9 +2043,8 @@
       <c r="J5" s="4" t="s">
         <v>140</v>
       </c>
-      <c r="K5" s="4" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
+      <c r="K5" s="8" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2073,9 +2078,8 @@
       <c r="J6" s="3" t="s">
         <v>143</v>
       </c>
-      <c r="K6" s="3" t="b">
-        <f aca="false">TRUE()</f>
-        <v>1</v>
+      <c r="K6" s="7" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2109,9 +2113,8 @@
       <c r="J7" s="4" t="s">
         <v>140</v>
       </c>
-      <c r="K7" s="4" t="b">
-        <f aca="false">TRUE()</f>
-        <v>1</v>
+      <c r="K7" s="8" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2143,9 +2146,8 @@
       <c r="J8" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="K8" s="3" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
+      <c r="K8" s="7" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2177,9 +2179,8 @@
       <c r="J9" s="4" t="s">
         <v>151</v>
       </c>
-      <c r="K9" s="4" t="b">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
+      <c r="K9" s="8" t="s">
+        <v>44</v>
       </c>
     </row>
   </sheetData>

--- a/Arquivo.xlsx
+++ b/Arquivo.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:D5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -518,6 +518,28 @@
       <c r="D4" t="inlineStr">
         <is>
           <t>Testador</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>U004</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>.@</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>teste 1</t>
         </is>
       </c>
     </row>
@@ -1973,8 +1995,10 @@
           <t>P001</t>
         </is>
       </c>
-      <c r="E10" t="n">
-        <v>20</v>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">

--- a/Arquivo.xlsx
+++ b/Arquivo.xlsx
@@ -778,7 +778,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H6"/>
+  <dimension ref="A1:H8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1012,6 +1012,82 @@
         </is>
       </c>
       <c r="H6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>U004</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>S001</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>2026-1</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Engenharia de Sistemas</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>U004</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>S002</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>2026-2</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Engenharia de Sistemas</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Arquivo.xlsx
+++ b/Arquivo.xlsx
@@ -778,7 +778,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H8"/>
+  <dimension ref="A1:H9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1088,6 +1088,44 @@
         </is>
       </c>
       <c r="H8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>U004</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>S003</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>2027-1</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Engenharia de Sistemas</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>2027</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Arquivo.xlsx
+++ b/Arquivo.xlsx
@@ -22,16 +22,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -42,7 +39,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -50,21 +47,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -434,22 +422,22 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>id_user</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>email</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>senha</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>nome</t>
         </is>
@@ -558,42 +546,42 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>id_user</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>id_eventos</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>titulo</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>descricao</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>data_inicio</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>data_final</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>local</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>organizador</t>
         </is>
@@ -669,7 +657,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-10-12 00:00:00</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -679,7 +667,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>IEEE UFMG</t>
+          <t xml:space="preserve">IEEE </t>
         </is>
       </c>
     </row>
@@ -778,46 +766,46 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H9"/>
+  <dimension ref="A1:H11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>id_user</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>id_semestre</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>titulo</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>descricao</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>ano</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>semestre_num</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>ativo</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>semestre_ano</t>
         </is>
@@ -1126,6 +1114,78 @@
         </is>
       </c>
       <c r="H9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>U001</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>S003</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>2027-1</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Ciência da Computação - UFMG</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>2027</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>U001</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>S004</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>2027-2</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Ciência da Computação - UFMG</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>2027</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1138,46 +1198,46 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H10"/>
+  <dimension ref="A1:H11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>id_user</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>id_semestre</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>id_materia</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>titulo</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>descricao</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>professor</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>sala</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>horario</t>
         </is>
@@ -1558,6 +1618,48 @@
       <c r="H10" t="inlineStr">
         <is>
           <t>TER-19h/QUI-20h55</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>U001</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>S003</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>M001</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Cálculo 3</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Integral de Linha e Integral de Superficia</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Rogerio</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>413 CAD 3</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Seg 10h</t>
         </is>
       </c>
     </row>
@@ -1572,61 +1674,61 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K10"/>
+  <dimension ref="A1:K11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>id_user</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>id_semestre</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>id_materia</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>id_prova</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>valor_nota</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>nota_obtida</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>titulo</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>dia</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>conteudo</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>sala</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>duracao</t>
         </is>
@@ -2138,6 +2240,59 @@
       <c r="K10" t="inlineStr">
         <is>
           <t>1h40</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>U001</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>S003</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>M001</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>P001</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Prova 1</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>2027-03-10</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Integral de Linha</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>423 CAD 3</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>60</t>
         </is>
       </c>
     </row>
@@ -2156,57 +2311,57 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>id_user</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>id_semestre</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>id_materia</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>id_trabalho</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>valor_nota</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>nota_obtida</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>titulo</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>data_entrega</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>descricao_tarefa</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>grupo</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>entregue</t>
         </is>
